--- a/dataset_t6_grouped/results2/G4/G4_T1936_W0015F0002T0006Z000C1N108_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T1936_W0015F0002T0006Z000C1N108_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>60.66381938173154</v>
+        <v>9.857870649531375</v>
       </c>
       <c r="D2" t="n">
-        <v>61.03823865784732</v>
+        <v>9.918713781900189</v>
       </c>
       <c r="E2" t="n">
-        <v>16.24370552257709</v>
+        <v>2.639602147418777</v>
       </c>
       <c r="F2" t="n">
-        <v>16.2989228438219</v>
+        <v>2.648574962121059</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>70.25705921784441</v>
+        <v>11.41677212289972</v>
       </c>
       <c r="D3" t="n">
-        <v>69.79542920222978</v>
+        <v>11.34175724536234</v>
       </c>
       <c r="E3" t="n">
-        <v>16.24370552257709</v>
+        <v>2.639602147418777</v>
       </c>
       <c r="F3" t="n">
-        <v>16.2989228438219</v>
+        <v>2.648574962121059</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>54.74584156344116</v>
+        <v>8.896199254059189</v>
       </c>
       <c r="D4" t="n">
-        <v>53.95416891404091</v>
+        <v>8.767552448531649</v>
       </c>
       <c r="E4" t="n">
-        <v>16.24370552257709</v>
+        <v>2.639602147418777</v>
       </c>
       <c r="F4" t="n">
-        <v>16.2989228438219</v>
+        <v>2.648574962121059</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>20.40661923284493</v>
+        <v>3.316075625337302</v>
       </c>
       <c r="D5" t="n">
-        <v>20.52480675492696</v>
+        <v>3.335281097675632</v>
       </c>
       <c r="E5" t="n">
-        <v>16.24370552257709</v>
+        <v>2.639602147418777</v>
       </c>
       <c r="F5" t="n">
-        <v>16.2989228438219</v>
+        <v>2.648574962121059</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>52.40967113003681</v>
+        <v>8.516571558630982</v>
       </c>
       <c r="D6" t="n">
-        <v>52.14608846800598</v>
+        <v>8.473739376050974</v>
       </c>
       <c r="E6" t="n">
-        <v>16.24370552257709</v>
+        <v>2.639602147418777</v>
       </c>
       <c r="F6" t="n">
-        <v>16.2989228438219</v>
+        <v>2.648574962121059</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>54.66033135511478</v>
+        <v>8.882303845206152</v>
       </c>
       <c r="D7" t="n">
-        <v>54.76749443654471</v>
+        <v>8.899717845938515</v>
       </c>
       <c r="E7" t="n">
-        <v>16.24370552257709</v>
+        <v>2.639602147418777</v>
       </c>
       <c r="F7" t="n">
-        <v>16.2989228438219</v>
+        <v>2.648574962121059</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>76.27057423871955</v>
+        <v>12.39396831379193</v>
       </c>
       <c r="D8" t="n">
-        <v>76.74484177037596</v>
+        <v>12.47103678768609</v>
       </c>
       <c r="E8" t="n">
-        <v>16.24370552257709</v>
+        <v>2.639602147418777</v>
       </c>
       <c r="F8" t="n">
-        <v>16.2989228438219</v>
+        <v>2.648574962121059</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>70.47301542533634</v>
+        <v>11.45186500661716</v>
       </c>
       <c r="D9" t="n">
-        <v>70.74084684930772</v>
+        <v>11.4953876130125</v>
       </c>
       <c r="E9" t="n">
-        <v>16.24370552257709</v>
+        <v>2.639602147418777</v>
       </c>
       <c r="F9" t="n">
-        <v>16.2989228438219</v>
+        <v>2.648574962121059</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
